--- a/public/templates/forms/A-020-RTORPODocumentation-FORM.xlsx
+++ b/public/templates/forms/A-020-RTORPODocumentation-FORM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
@@ -526,7 +526,7 @@
     <row r="2" ht="29.75" customHeight="1">
       <c r="A2" s="8" t="n"/>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -571,7 +571,7 @@
       <c r="D5" s="22" t="n"/>
       <c r="E5" s="21" t="n"/>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6" ht="50.5" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Classification</t>
@@ -628,14 +628,14 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="29.75" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>« Replace the corner, column headers, and row labels with the dimensions this matrix maps (e.g., role × system, control × artifact). Add rows and columns as needed. »</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>System or service \ Recovery attribute</t>
@@ -662,7 +662,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>[9-1-1 call handling / call delivery]</t>
@@ -689,7 +689,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>[Computer-aided dispatch (CAD)]</t>
@@ -838,7 +838,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="80" customHeight="1">
+    <row r="27" ht="82.2" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Targets derive from the Asset Criticality Ranking Matrix: the criticality tier sets the recovery order. The Backup Schedule &amp; Media Inventory and Restoration Test Records must meet these targets; the RTO Compliance Matrix verifies whether they are met. Where recovery depends on a third party such as the CAD vendor or ESInet provider, record the contractual restoration commitment in the dependency column and confirm it against the IT Support Accountability Agreement.</t>
@@ -987,7 +987,7 @@
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1013,14 +1013,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: replace every [BRACKETED] field with your agency's information and follow the « » guidance notes, then delete every « » note before publishing. This sheet explains each column; it is guidance only and can be removed once the record is populated.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule and revision history live on the Matrix tab.</t>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Corner cell</t>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Column headers</t>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Row labels</t>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Cells</t>
@@ -1230,6 +1230,6 @@
     <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>